--- a/data/2nd Round/Corrected/Mo_400Sb_30Se_Results Table.xlsx
+++ b/data/2nd Round/Corrected/Mo_400Sb_30Se_Results Table.xlsx
@@ -2,23 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Corrected Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,10 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,8 +415,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -511,6 +509,16 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Rseriescm2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Rshuntcm2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -551,9 +559,6 @@
       <c r="L2" t="n">
         <v>4.627e-05</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>14.571</v>
       </c>
@@ -565,6 +570,12 @@
       <c r="R2" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S2" t="n">
+        <v>8.372663763700192</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8.784094057406893</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,9 +616,6 @@
       <c r="L3" t="n">
         <v>5.045e-05</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>14.549</v>
       </c>
@@ -619,6 +627,12 @@
       <c r="R3" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S3" t="n">
+        <v>10.66125851705404</v>
+      </c>
+      <c r="T3" t="n">
+        <v>11.0672509788285</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -659,9 +673,6 @@
       <c r="L4" t="n">
         <v>5.623e-05</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>14.562</v>
       </c>
@@ -673,6 +684,12 @@
       <c r="R4" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S4" t="n">
+        <v>9.975156512797268</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10.63183095284817</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -713,9 +730,6 @@
       <c r="L5" t="n">
         <v>7.46e-05</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>14.558</v>
       </c>
@@ -727,6 +741,12 @@
       <c r="R5" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S5" t="n">
+        <v>7.853095093718603</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8.558983438983798</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -767,9 +787,6 @@
       <c r="L6" t="n">
         <v>0.00036785</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>14.562</v>
       </c>
@@ -781,6 +798,12 @@
       <c r="R6" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S6" t="n">
+        <v>16.81960782964154</v>
+      </c>
+      <c r="T6" t="n">
+        <v>29.73729192511558</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -821,9 +844,6 @@
       <c r="L7" t="n">
         <v>0.00012975</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>14.548</v>
       </c>
@@ -835,6 +855,12 @@
       <c r="R7" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S7" t="n">
+        <v>11.9940353811483</v>
+      </c>
+      <c r="T7" t="n">
+        <v>13.19438630222652</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -875,9 +901,6 @@
       <c r="L8" t="n">
         <v>0.00017543</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>14.548</v>
       </c>
@@ -889,6 +912,12 @@
       <c r="R8" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S8" t="n">
+        <v>10.08042711235501</v>
+      </c>
+      <c r="T8" t="n">
+        <v>13.43883989323045</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -929,9 +958,6 @@
       <c r="L9" t="n">
         <v>5.957e-05</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>14.804</v>
       </c>
@@ -943,6 +969,12 @@
       <c r="R9" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S9" t="n">
+        <v>11.88559376474818</v>
+      </c>
+      <c r="T9" t="n">
+        <v>13.91061784973458</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -983,9 +1015,6 @@
       <c r="L10" t="n">
         <v>0.0002922</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>14.804</v>
       </c>
@@ -997,6 +1026,12 @@
       <c r="R10" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S10" t="n">
+        <v>12.73569167182101</v>
+      </c>
+      <c r="T10" t="n">
+        <v>27.1556174795204</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1037,9 +1072,6 @@
       <c r="L11" t="n">
         <v>0.00032643</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>14.563</v>
       </c>
@@ -1051,6 +1083,12 @@
       <c r="R11" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S11" t="n">
+        <v>13.0934393739958</v>
+      </c>
+      <c r="T11" t="n">
+        <v>30.32653930075563</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1091,9 +1129,6 @@
       <c r="L12" t="n">
         <v>0.00026518</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>14.553</v>
       </c>
@@ -1105,7 +1140,14 @@
       <c r="R12" s="1" t="n">
         <v>46272</v>
       </c>
-    </row>
+      <c r="S12" t="n">
+        <v>9.821785659043993</v>
+      </c>
+      <c r="T12" t="n">
+        <v>26.24569475271079</v>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
